--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,2014 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131264650</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>430203</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7055994</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131264654</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>430837</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7056028</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131264652</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>430412</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7056002</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131264641</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>430554</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7055843</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131264664</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>430909</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7055916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131264642</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>430300</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7055882</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131264646</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>430167</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7055994</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131264660</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>430675</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7055751</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131264667</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79244</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>430553</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7055760</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131264661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91805</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>430447</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7055754</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131264653</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>430458</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7055903</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131264665</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>430816</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7055900</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131264651</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>430339</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7055930</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131264655</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>430882</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7055919</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131264663</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>430397</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056003</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131264648</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>430168</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7055992</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131264649</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>430123</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056053</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131264657</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>430617</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7055798</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131264643</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>430196</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7055979</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131264656</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>430811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7055889</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264652</v>
+        <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,23 +1011,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430412</v>
+        <v>430909</v>
       </c>
       <c r="R5" t="n">
-        <v>7056002</v>
+        <v>7055916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264641</v>
+        <v>131264652</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430554</v>
+        <v>430412</v>
       </c>
       <c r="R6" t="n">
-        <v>7055843</v>
+        <v>7056002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264664</v>
+        <v>131264641</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430909</v>
+        <v>430554</v>
       </c>
       <c r="R7" t="n">
-        <v>7055916</v>
+        <v>7055843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131264642</v>
+        <v>131264646</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430300</v>
+        <v>430167</v>
       </c>
       <c r="R8" t="n">
-        <v>7055882</v>
+        <v>7055994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131264646</v>
+        <v>131264642</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430167</v>
+        <v>430300</v>
       </c>
       <c r="R9" t="n">
-        <v>7055994</v>
+        <v>7055882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B12" t="n">
-        <v>91805</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R12" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>91805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R13" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B17" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,19 +2212,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2232,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R17" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,23 +2314,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R18" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,11 +2370,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131264646</v>
+        <v>131264642</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430167</v>
+        <v>430300</v>
       </c>
       <c r="R8" t="n">
-        <v>7055994</v>
+        <v>7055882</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131264642</v>
+        <v>131264646</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430300</v>
+        <v>430167</v>
       </c>
       <c r="R9" t="n">
-        <v>7055882</v>
+        <v>7055994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R10" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R11" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,7 +1810,7 @@
         <v>131264661</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,23 +1915,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R14" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,19 +2008,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R15" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,6 +2068,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,23 +2212,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R17" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,11 +2268,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2303,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,19 +2305,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2334,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R18" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,6 +2365,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2396,7 +2396,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131264649</v>
+        <v>131264657</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>430123</v>
+        <v>430617</v>
       </c>
       <c r="R19" t="n">
-        <v>7056053</v>
+        <v>7055798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264657</v>
+        <v>131264649</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430617</v>
+        <v>430123</v>
       </c>
       <c r="R20" t="n">
-        <v>7055798</v>
+        <v>7056053</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B5" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,19 +1011,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R5" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1071,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,23 +1215,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R7" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91806</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R12" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>91806</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R13" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264652</v>
+        <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,23 +1011,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430412</v>
+        <v>430909</v>
       </c>
       <c r="R5" t="n">
-        <v>7056002</v>
+        <v>7055916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264641</v>
+        <v>131264652</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430554</v>
+        <v>430412</v>
       </c>
       <c r="R6" t="n">
-        <v>7055843</v>
+        <v>7056002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264664</v>
+        <v>131264641</v>
       </c>
       <c r="B7" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430909</v>
+        <v>430554</v>
       </c>
       <c r="R7" t="n">
-        <v>7055916</v>
+        <v>7055843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R10" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R11" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R10" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R11" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R10" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R11" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,19 +1011,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R5" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1071,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,23 +1215,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R7" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R10" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R11" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,19 +2212,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2232,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R17" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,23 +2314,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R18" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,11 +2370,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R5" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,23 +1113,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R6" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B7" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R7" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,23 +1915,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R14" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,19 +2008,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R15" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,6 +2068,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,23 +2212,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R17" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,11 +2268,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2303,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,19 +2305,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2334,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R18" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,6 +2365,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131264657</v>
+        <v>131264649</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>430617</v>
+        <v>430123</v>
       </c>
       <c r="R19" t="n">
-        <v>7055798</v>
+        <v>7056053</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264649</v>
+        <v>131264657</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430123</v>
+        <v>430617</v>
       </c>
       <c r="R20" t="n">
-        <v>7056053</v>
+        <v>7055798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264641</v>
+        <v>131264652</v>
       </c>
       <c r="B5" t="n">
         <v>57887</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430554</v>
+        <v>430412</v>
       </c>
       <c r="R5" t="n">
-        <v>7055843</v>
+        <v>7056002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264664</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1113,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1133,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430909</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7055916</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264652</v>
+        <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,23 +1215,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430412</v>
+        <v>430909</v>
       </c>
       <c r="R7" t="n">
-        <v>7056002</v>
+        <v>7055916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B12" t="n">
-        <v>91813</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R12" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R13" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,19 +2212,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2232,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R17" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,23 +2314,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R18" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,11 +2370,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131264642</v>
+        <v>131264646</v>
       </c>
       <c r="B8" t="n">
         <v>57887</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430300</v>
+        <v>430167</v>
       </c>
       <c r="R8" t="n">
-        <v>7055882</v>
+        <v>7055994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131264646</v>
+        <v>131264642</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430167</v>
+        <v>430300</v>
       </c>
       <c r="R9" t="n">
-        <v>7055994</v>
+        <v>7055882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R12" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R13" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264648</v>
+        <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,23 +2212,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430168</v>
+        <v>430397</v>
       </c>
       <c r="R17" t="n">
-        <v>7055992</v>
+        <v>7056003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,11 +2268,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2303,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264663</v>
+        <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,19 +2305,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2334,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430397</v>
+        <v>430168</v>
       </c>
       <c r="R18" t="n">
-        <v>7056003</v>
+        <v>7055992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,6 +2365,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131264652</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131264646</v>
+        <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430167</v>
+        <v>430300</v>
       </c>
       <c r="R8" t="n">
-        <v>7055994</v>
+        <v>7055882</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131264642</v>
+        <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430300</v>
+        <v>430167</v>
       </c>
       <c r="R9" t="n">
-        <v>7055882</v>
+        <v>7055994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,7 +1504,7 @@
         <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,23 +1915,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R14" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,19 +2008,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R15" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,6 +2068,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131264649</v>
+        <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>430123</v>
+        <v>430617</v>
       </c>
       <c r="R19" t="n">
-        <v>7056053</v>
+        <v>7055798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264657</v>
+        <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430617</v>
+        <v>430123</v>
       </c>
       <c r="R20" t="n">
-        <v>7055798</v>
+        <v>7056053</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R5" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,23 +1113,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R6" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R7" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,23 +1011,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R5" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1104,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R6" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B7" t="n">
         <v>57888</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R7" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264664</v>
+        <v>131264641</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,19 +1011,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430909</v>
+        <v>430554</v>
       </c>
       <c r="R5" t="n">
-        <v>7055916</v>
+        <v>7055843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1071,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1105,7 @@
         <v>131264652</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,23 +1215,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R7" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R10" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R11" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R12" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R13" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,23 +1915,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R14" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,19 +2008,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R15" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,6 +2068,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,23 +1011,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R5" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R7" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R10" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R11" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R12" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R13" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,7 +1907,7 @@
         <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R12" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>91818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R13" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91842</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264641</v>
+        <v>131264652</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430554</v>
+        <v>430412</v>
       </c>
       <c r="R6" t="n">
-        <v>7055843</v>
+        <v>7056002</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R7" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131264667</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131264660</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264653</v>
+        <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>91824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430458</v>
+        <v>430447</v>
       </c>
       <c r="R12" t="n">
-        <v>7055903</v>
+        <v>7055754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264661</v>
+        <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>91818</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430447</v>
+        <v>430458</v>
       </c>
       <c r="R13" t="n">
-        <v>7055754</v>
+        <v>7055903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,23 +1915,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R14" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>91842</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,19 +2008,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R15" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,6 +2068,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131264664</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131264652</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131264641</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264667</v>
+        <v>131264660</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430553</v>
+        <v>430675</v>
       </c>
       <c r="R10" t="n">
-        <v>7055760</v>
+        <v>7055751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264660</v>
+        <v>131264667</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430675</v>
+        <v>430553</v>
       </c>
       <c r="R11" t="n">
-        <v>7055751</v>
+        <v>7055760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>131264665</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131264650</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131264654</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264664</v>
+        <v>131264652</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,19 +1011,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430909</v>
+        <v>430412</v>
       </c>
       <c r="R5" t="n">
-        <v>7055916</v>
+        <v>7056002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1071,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264641</v>
+        <v>131264664</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,23 +1215,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430554</v>
+        <v>430909</v>
       </c>
       <c r="R7" t="n">
-        <v>7055843</v>
+        <v>7055916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1300,7 @@
         <v>131264642</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>131264646</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131264660</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>131264667</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131264661</v>
       </c>
       <c r="B12" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131264653</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264651</v>
       </c>
       <c r="B14" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1915,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430339</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131264651</v>
+        <v>131264665</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,23 +2017,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2032,10 +2037,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430339</v>
+        <v>430816</v>
       </c>
       <c r="R15" t="n">
-        <v>7055930</v>
+        <v>7055900</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,11 +2073,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>131264655</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131264663</v>
       </c>
       <c r="B17" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>131264648</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>131264649</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>131264643</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>131264656</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89592714</v>
+        <v>131264661</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höbäcken, Jmt</t>
+          <t>Gräslottsstenen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430928.0611863565</v>
+        <v>430447</v>
       </c>
       <c r="R2" t="n">
-        <v>7055949.156582703</v>
+        <v>7055754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,57 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131264650</v>
+        <v>131264667</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430203</v>
+        <v>430553</v>
       </c>
       <c r="R3" t="n">
-        <v>7055994</v>
+        <v>7055760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,27 +874,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131264654</v>
+        <v>131264659</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430837</v>
+        <v>430261</v>
       </c>
       <c r="R4" t="n">
-        <v>7056028</v>
+        <v>7055860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,30 +976,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131264664</v>
+        <v>131264660</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430909</v>
+        <v>430675</v>
       </c>
       <c r="R5" t="n">
-        <v>7055916</v>
+        <v>7055751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131264652</v>
+        <v>131264641</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430412</v>
+        <v>430554</v>
       </c>
       <c r="R6" t="n">
-        <v>7056002</v>
+        <v>7055843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131264641</v>
+        <v>131264642</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430554</v>
+        <v>430300</v>
       </c>
       <c r="R7" t="n">
-        <v>7055843</v>
+        <v>7055882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131264642</v>
+        <v>131264643</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430300</v>
+        <v>430196</v>
       </c>
       <c r="R8" t="n">
-        <v>7055882</v>
+        <v>7055979</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131264646</v>
+        <v>131264644</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430167</v>
+        <v>430144</v>
       </c>
       <c r="R9" t="n">
-        <v>7055994</v>
+        <v>7055944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131264660</v>
+        <v>131264645</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,16 +1497,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1536,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430675</v>
+        <v>430148</v>
       </c>
       <c r="R10" t="n">
-        <v>7055751</v>
+        <v>7055943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131264667</v>
+        <v>131264646</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430553</v>
+        <v>430167</v>
       </c>
       <c r="R11" t="n">
-        <v>7055760</v>
+        <v>7055994</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131264653</v>
+        <v>131264648</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430458</v>
+        <v>430168</v>
       </c>
       <c r="R12" t="n">
-        <v>7055903</v>
+        <v>7055992</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131264661</v>
+        <v>131264649</v>
       </c>
       <c r="B13" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1803,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430447</v>
+        <v>430123</v>
       </c>
       <c r="R13" t="n">
-        <v>7055754</v>
+        <v>7056053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131264665</v>
+        <v>131264650</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,19 +1905,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1935,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430816</v>
+        <v>430203</v>
       </c>
       <c r="R14" t="n">
-        <v>7055900</v>
+        <v>7055994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1965,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,7 +1999,7 @@
         <v>131264651</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131264655</v>
+        <v>131264652</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430882</v>
+        <v>430412</v>
       </c>
       <c r="R16" t="n">
-        <v>7055919</v>
+        <v>7056002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,7 +2173,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131264663</v>
+        <v>131264653</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2212,19 +2211,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2232,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430397</v>
+        <v>430458</v>
       </c>
       <c r="R17" t="n">
-        <v>7056003</v>
+        <v>7055903</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,6 +2271,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131264648</v>
+        <v>131264656</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430168</v>
+        <v>430811</v>
       </c>
       <c r="R18" t="n">
-        <v>7055992</v>
+        <v>7055889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,7 +2377,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,7 +2407,7 @@
         <v>131264657</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264649</v>
+        <v>131264658</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430123</v>
+        <v>430332</v>
       </c>
       <c r="R20" t="n">
-        <v>7056053</v>
+        <v>7055694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2600,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131264643</v>
+        <v>89592667</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2611,34 +2619,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gräslottsstenen, Jmt</t>
+          <t>Höbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430196</v>
+        <v>430960</v>
       </c>
       <c r="R21" t="n">
-        <v>7055979</v>
+        <v>7055946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,17 +2673,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2686,26 +2689,35 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131264656</v>
+        <v>89592711</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,34 +2725,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gräslottsstenen, Jmt</t>
+          <t>Höbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430811</v>
+        <v>430907</v>
       </c>
       <c r="R22" t="n">
-        <v>7055889</v>
+        <v>7055798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2767,17 +2779,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,19 +2795,545 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>89592716</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>430970</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7055942</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>89592676</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>430865</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7055822</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>89592714</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>430928</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7055949</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131264654</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>430837</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7056028</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131264655</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gräslottsstenen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>430882</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7055919</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2452-2026 artfynd.xlsx
+++ b/artfynd/A 2452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592667</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592711</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592676</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264659</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264660</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264641</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264642</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264643</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264644</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264645</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264646</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264648</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264649</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264650</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264651</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264652</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2824,6 +2929,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264653</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264654</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264655</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,6 +3250,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264656</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264657</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,8 +3464,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131264658</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>